--- a/www/download/COUNTRY.TWN.zdW16.xlsx
+++ b/www/download/COUNTRY.TWN.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>China: Taiwan</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>31.2251998907558</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>33.8003000414591</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>34.5750000280065</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>34.4180000256075</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>33.4219999327801</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>32.1669997893536</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>32.5309998875923</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>32.8419998496038</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>31.5169996491601</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>33.04900014051</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>31.6419998794869</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>29.4640003347948</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>29.613999580481</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>29.7699998521127</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.3680001622391</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>16.928</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17.059</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>18.078</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>18.115</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>18.342</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>18.565</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>19.007</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>19.236</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>19.036</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>19.723</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>19.581</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>19.902</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>20.227</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>20.207</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>6.811</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6.605</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>6.545</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>6.747</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>7.011</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>7.166</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>7.343</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>7.514</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>7.657</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>7.475</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>7.714</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>7.959</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>8.072</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>8.169</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>8.308</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>36696.374</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>35770.452</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>38234.799</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>38292.743</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>38946.251</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>39321.375</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>40260.13</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>40600.85</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>39997.486</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>40087.459</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>41586.89</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>40801.467</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>41456.613</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>41808.076</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>41977.788</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15199.571</t>
+          <t>43493951502.9625</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14088.907</t>
+          <t>38979197809.7149</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14066.893</t>
+          <t>40969354838.7649</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>14498.192</t>
+          <t>43482041368.9089</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15201.776</t>
+          <t>47803436727.6776</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>15418.961</t>
+          <t>47029762660.7121</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>15772.77</t>
+          <t>48553896283.0045</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>16100.269</t>
+          <t>48597904780.0074</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>16307.196</t>
+          <t>47911811999.766</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>15704.182</t>
+          <t>41813361075.0403</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>16541.346</t>
+          <t>47843650530.2676</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>16859.794</t>
+          <t>50058323869.3525</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>17063.268</t>
+          <t>48772816719.9938</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>17138.589</t>
+          <t>49057862823.9945</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>17498.639</t>
+          <t>51222587648.5545</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10780717674.0855</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10367090661.6016</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>10778884629.5732</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>11127525839.8045</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>11374760760.72</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>11344418858.5308</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>11250984312.7903</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>10794941479.8897</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>10382556073.5253</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>9837274038.85605</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>10258288116.8191</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>10285508979.5351</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>10052335439.812</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>9527854155.24815</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>10279232560.6949</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4526957.03960649</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4658999.77848312</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4671003.6332242</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>4683213.37893568</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4366297.89328639</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3942325.72469155</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3727554.34558179</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3549106.62135144</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>3309200.90646031</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3386497.20201467</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3100298.0425067</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2783028.1419102</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2798213.91974234</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2743520.84907233</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2765683.80044569</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>169110.132286262</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>154342.106649144</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>164734.86547853</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>182381.612173994</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>205664.106879143</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>220004.331446212</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>239708.244365677</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>271446.609487661</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>288868.336056005</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>263273.632033985</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>308311.498269664</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>318562.424625418</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>315631.410782688</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>317522.910665935</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>325383.737309706</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>394548.412859476</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>348415.976076262</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>368898.717942572</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>426251.91354656</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>516422.507003349</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>548751.982341553</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>598665.15374457</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>672172.18759616</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>722762.724790332</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>576454.219388243</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>728732.599893296</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>812958.180368377</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>773716.862364672</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>773726.245413551</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>810687.946558191</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.409884894447838</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.359002970060208</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.305041614547547</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.302912454099922</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.336447976338599</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.359167110477873</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.4019013413848</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.491464222385441</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.570634040839145</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.59639570250563</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.612486002696638</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.639179357438276</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.697443156584424</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.798787924409999</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.702329322415584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>31.2251998907558</t>
+          <t>1582.83476732124</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>33.8003000414591</t>
+          <t>1569.62477281392</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>34.5750000280065</t>
+          <t>1646.9699385536</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>34.4180000256075</t>
+          <t>1649.30032771081</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>33.4219999327801</t>
+          <t>1622.52647030665</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>32.1669997893536</t>
+          <t>1583.13604524649</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>32.5309998875923</t>
+          <t>1532.30640733915</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>32.8419998496038</t>
+          <t>1436.71224685574</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>31.5169996491601</t>
+          <t>1356.03865581022</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>33.04900014051</t>
+          <t>1315.95744090611</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>31.6419998794869</t>
+          <t>1329.84302988525</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>29.4640003347948</t>
+          <t>1292.33282859691</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>29.613999580481</t>
+          <t>1245.29011117696</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>29.7699998521127</t>
+          <t>1166.33049955015</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>30.3680001622391</t>
+          <t>1237.21961561903</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>6785737804.76652</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>7450794039.10389</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>7982497347.87256</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>8349466635.03588</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>8443924325.47011</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>8843986914.64406</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>8679110886.06406</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>7983496798.61007</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>7084765520.81002</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>6157754191.58001</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>6407147459.8754</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>7646866577.17116</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>7515036335.17536</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>7454663619.98022</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>8826209089.41228</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>6602460748.02028</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>7070733969.88301</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>7430788479.66183</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>7977391174.99005</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>7969250467.48807</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>8330437452.45555</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.587</t>
+          <t>7953844208.37856</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>7268910840.45867</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>6459972036.87285</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>5471238363.67062</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>5765328485.05454</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>6921962028.0835</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>6640424035.39357</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>6368436003.63378</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>7565486059.09346</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>183277056.74624</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>380060069.220874</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>551708868.21073</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>372075460.045827</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>474673857.982047</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>513549462.188513</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>725266677.685498</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.021</t>
+          <t>714585958.151393</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.184</t>
+          <t>624793483.937166</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.109</t>
+          <t>686515827.909397</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>641818974.820861</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1.393</t>
+          <t>724904549.087653</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>874612299.781788</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1086227616.34644</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.479</t>
+          <t>1260723030.31882</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>2231.61482885307</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>2133.12472813419</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>2149.36430772127</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>2148.89393752549</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>2168.42221779713</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>2151.74644411104</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>2148.14240786128</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>2142.80491404834</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2129.84047350929</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>2100.78880334282</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>2144.35327147365</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.187</t>
+          <t>2118.36529557588</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>2113.80917717959</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.194</t>
+          <t>2097.98121846189</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>2106.15522993602</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>2167.78299969258</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>2096.82640563694</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>2115.03840778263</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>2113.81190442449</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2123.36835266888</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>2118.09192888322</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>2118.16716194603</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>2110.63651485328</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>2101.11262472953</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>2080.28820115789</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>2108.55902266873</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>2083.75448926407</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>2083.0268469795</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>2066.92814170573</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>2077.40448627921</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>170933.951110638</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>145320.207593522</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>156005.444199202</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>171063.198636918</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>207567.097193707</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>226408.747320097</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>254041.885815983</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>283190.635708391</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>291566.759583149</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>236014.492517203</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>315573.892706619</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>352918.270945234</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>348644.813195935</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>354642.934642871</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>369923.222015293</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>11837196914.1108</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10465130905.1927</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>11393486189.6539</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>12337621667.6552</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>13755574286.0363</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>13550076868.6371</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>14450743531.0734</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>14912239993.5393</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>14160021610.5537</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>12058340764.7583</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>14415165643.5746</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>14986774627.8268</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>14419179517.9349</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>14763747371.7243</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>15421188238.2162</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>153530.731840536</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>121146.950334633</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>125658.742384143</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>139611.41613121</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>182351.265541939</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>196863.71781806</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>216207.984437174</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>232880.76712955</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>249443.965352613</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>185914.03227066</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>263832.350704573</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>298447.925303675</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>289158.196750193</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>286185.943263742</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>293299.751876012</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>36696.374</t>
+          <t>16242959385.9705</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>35770.452</t>
+          <t>14475324092.1104</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>38234.799</t>
+          <t>15029469818.9121</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>38292.743</t>
+          <t>16440790481.1013</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>38946.251</t>
+          <t>19097350223.8626</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>39321.375</t>
+          <t>19097453964.6409</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>40260.13</t>
+          <t>19298648257.5333</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>40600.85</t>
+          <t>18527258544.352</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>39997.486</t>
+          <t>18051508621.0612</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>40087.459</t>
+          <t>13949955046.1411</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>41586.89</t>
+          <t>16894741804.9166</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>40801.467</t>
+          <t>18719359975.2024</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>41456.613</t>
+          <t>17630984262.1245</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>41808.076</t>
+          <t>17216891465.8202</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>41977.788</t>
+          <t>18702994337.7387</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>15199.571</t>
+          <t>17403.2192701016</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14088.907</t>
+          <t>24173.2572588888</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>14066.893</t>
+          <t>30346.7018150584</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>14498.192</t>
+          <t>31451.7825057074</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>15201.776</t>
+          <t>25215.8316517685</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>15418.961</t>
+          <t>29545.029502037</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>15772.77</t>
+          <t>37833.9013788097</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>16100.269</t>
+          <t>50309.8685788409</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>16307.196</t>
+          <t>42122.7942305353</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>15704.182</t>
+          <t>50100.460246543</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>16541.346</t>
+          <t>51741.5420020457</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>16859.794</t>
+          <t>54470.3456415584</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>17063.268</t>
+          <t>59486.6164457416</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>17138.589</t>
+          <t>68456.9913791289</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>17498.639</t>
+          <t>76623.4701392806</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>50310.319</t>
+          <t>-4405762471.85977</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>45542.621</t>
+          <t>-4010193186.9177</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>48126.025</t>
+          <t>-3635983629.25818</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>51167.487</t>
+          <t>-4103168813.44603</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>56382.533</t>
+          <t>-5341775937.82622</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>56243.163</t>
+          <t>-5547377096.00375</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>58235.921</t>
+          <t>-4847904726.45987</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>57594.04</t>
+          <t>-3615018550.81276</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>57245.782</t>
+          <t>-3891487010.50755</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>50293.077</t>
+          <t>-1891614281.38274</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>56740.112</t>
+          <t>-2479576161.34201</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>60078.166</t>
+          <t>-3732585347.37565</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>59053.763</t>
+          <t>-3211804744.1896</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>59248.559</t>
+          <t>-2453144094.09588</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>51222.588</t>
+          <t>-3281806099.52246</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>140966.462985025</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>124063.425472555</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>132659.146782357</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>140661.369051078</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>154571.629465622</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>164095.252898934</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>168585.226399434</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>176347.847268741</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>174670.685661706</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>166387.424732972</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>198916.376967322</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>213489.275047516</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>215034.308097521</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>225878.871346994</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>239319.217597471</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>18642.244</t>
+          <t>-0.281460892780487</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>17267.094</t>
+          <t>-0.310009006609538</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>18295.214</t>
+          <t>-0.343246737638383</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18604.784</t>
+          <t>-0.291095982970204</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>19037.612</t>
+          <t>-0.236746588444664</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>18855.06</t>
+          <t>-0.237125144891765</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>19441.2</t>
+          <t>-0.220933855907597</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>19625.532</t>
+          <t>-0.188450743482354</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>19149.03</t>
+          <t>-0.161647726124875</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>19096.669</t>
+          <t>-0.169379077036503</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>20241.646</t>
+          <t>-0.156699572199989</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>19615.647</t>
+          <t>-0.141626429673909</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>19896.468</t>
+          <t>-0.145738495829185</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>20132.438</t>
+          <t>-0.14178760274009</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>20559.078</t>
+          <t>-0.130840450919422</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>170774.341247462</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>155394.949713671</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>159055.676782522</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>164509.213127444</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>179193.528410636</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>192719.072075031</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>199054.924746032</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>204728.28348972</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>211248.566539354</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>196274.535101574</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>222132.44770931</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>242611.077307756</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>245906.89339446</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>252814.559450188</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>259777.36864169</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>12095.022</t>
+          <t>512506.974176429</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11602.969</t>
+          <t>490727.451099204</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>12141.184</t>
+          <t>523342.817449876</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>12565.577</t>
+          <t>513397.343549848</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>12839.887</t>
+          <t>534008.453688601</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>12885.79</t>
+          <t>575227.885146496</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>12786.862</t>
+          <t>587147.94261415</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>12125.91</t>
+          <t>584469.817944494</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>11653.859</t>
+          <t>592988.352785281</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>11075.042</t>
+          <t>565572.91012444</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>11448.859</t>
+          <t>624266.422881021</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>11542.618</t>
+          <t>668477.954374237</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>11305.473</t>
+          <t>684812.939121424</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>10741.856</t>
+          <t>699785.808310394</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>10279.233</t>
+          <t>704467.922649437</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>677024.512003141</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>640830.069077162</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>653015.193307648</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>694141.77058884</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>817476.028520209</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>879770.747430619</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>947568.095251788</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>1021361.04184221</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>1183648.78102227</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>1109101.8251892</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>44.48</t>
+          <t>1226245.50895792</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>1392500.59039185</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>1430472.33325257</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>59.55</t>
+          <t>1448319.78776885</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>70.23</t>
+          <t>1479244.17096199</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.157</t>
+          <t>530300.505530696</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5.338</t>
+          <t>546953.444947655</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>5.377</t>
+          <t>601227.456002399</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>5.392</t>
+          <t>586321.413017862</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5.039</t>
+          <t>580702.717714073</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>4.604</t>
+          <t>594481.312342776</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>4.374</t>
+          <t>619009.894642108</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>4.119</t>
+          <t>625958.729374222</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3.911</t>
+          <t>604510.345075002</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>3.959</t>
+          <t>599608.056793553</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>3.567</t>
+          <t>632599.252516674</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>3.251</t>
+          <t>632975.766220799</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>646174.717801961</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>3.199</t>
+          <t>657323.213839576</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2.766</t>
+          <t>658936.353471284</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>167448.095919066</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>164109.400958863</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>172746.063148668</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>178278.744328485</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>187168.282057555</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>193483.472679108</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>202527.916054168</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>212967.562531245</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>212103.126608484</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>207062.370573468</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>225097.515345503</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>232961.244999094</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>235906.259497371</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>240509.025559195</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>246923.682945132</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-190555.923582678</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-198663.093120132</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-224145.334731148</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>-202061.881030236</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-193534.660887452</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>-208615.765956022</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>-209349.873018995</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>-192476.247699076</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>-191334.13398273</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>-187858.643490049</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>-192152.146665864</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>-197214.886936008</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>-208474.886173494</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>-205353.790708782</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>-193544.974348593</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>15199571000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>14088907000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>14066893000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>14498192000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>15201776000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>15418961000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>15772770000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>16100269000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>16307196000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>15704182000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>16541346000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>16859794000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>17063268000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>17138589000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>17498639000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>36696373692.474</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>35770451509.648</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>38234799285.1855</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>38292742644.1067</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>38946251138.5658</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>39321374802.2346</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>40260130337.1378</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>40600849854.4912</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>39997485898.1932</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>40087459438.6781</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>41586890313.957</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>40801467380.6395</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>41456612777.3244</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>41808075896.1437</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>41977788379.1441</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>18642244278.7469</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>17267094273.9098</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>18295214458.1776</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>18604784057.1434</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>19037611620.3775</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>18855059890.7979</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>19441200414.4775</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>19625531558.9802</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>19149030428.7835</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>19096669028.5602</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>20241646359.4972</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>19615647409.1686</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>19896468201.7249</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>20132437651.2511</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>20559078341.4519</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>16928066</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>17059329</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>18077591</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>18115492</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>18341731</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>18564527</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>19007060</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>19236306</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>19036336</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>19270147</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>19722896</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>19580746</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>19902102</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>20227155</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>20206844</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6811019</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6604821</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6544676</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>6746816</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>7010524</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>7165789</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>7342516</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>7513642</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>7656534</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>7475374</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>7713909</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>7958870</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>8072284</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>8169086</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>8308333</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>36696373692.474</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>35770451509.648</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>38234799285.1855</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>38292742644.1067</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>38946251138.5658</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>39321374802.2346</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>40260130337.1378</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>40600849854.4912</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>39997485898.1932</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>40087459438.6781</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>41586890313.957</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>40801467380.6395</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>41456612777.3244</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>41808075896.1437</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>41977788379.1441</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>15199571000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>14088907000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>14066893000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>14498192000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>15201776000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>15418961000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>15772770000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>16100269000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>16307196000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>15704182000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>16541346000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>16859794000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>17063268000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>17138589000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>17498639000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>682643.217657533</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>599579.2049183</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>619819.031091829</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>658700.767040502</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>764161.031655796</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>829976.031336463</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>881079.862285205</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>937700.931733756</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>989540.692324777</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>855193.651850283</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1059649.95891537</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1187098.9342927</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1181257.17566016</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1193656.02955996</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1220628.55637513</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>321951.052355149</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>292064.3603755</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>299197.48373102</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>311335.464001395</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>340473.789719347</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>366612.11800914</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>377798.069533676</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>391993.575299921</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>401654.218358346</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>377714.272746528</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>432114.278490614</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>471263.066793375</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>476338.049571149</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>494432.012092711</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>510922.945205479</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>648133.185823473</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>659141.515478559</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>694990.42510201</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>739148.63116494</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>841844.737530497</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>871872.879197762</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>969644.347947842</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1070501.06077313</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>1314668.00256807</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1195147.04551319</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1242613.67741952</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1386536.33932696</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1450951.61349737</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>1449712.54301089</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1459349.7621078</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
